--- a/01_data/01_raw_files/species_lookup.xlsx
+++ b/01_data/01_raw_files/species_lookup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RIZZUTOM\Desktop\GitHub Projects\2026_Reddick_fish_morphology\01_data\01_raw_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A75BF43D-8E4F-4A4B-BFB5-FF750131473A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63CD4D69-65F9-4214-B365-C909A3FCCE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E8ECBFDF-D715-470C-9FD4-9B764B132C4E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{E8ECBFDF-D715-470C-9FD4-9B764B132C4E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
   <si>
     <t xml:space="preserve">Common Name </t>
   </si>
@@ -164,108 +164,27 @@
     <t>Alewife</t>
   </si>
   <si>
-    <t xml:space="preserve">White sucker </t>
-  </si>
-  <si>
-    <t>Longnose gar</t>
-  </si>
-  <si>
     <t>Bowfin</t>
   </si>
   <si>
-    <t xml:space="preserve">Bigmouth buffalo </t>
-  </si>
-  <si>
-    <t>Chinook salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gizzard shad </t>
-  </si>
-  <si>
-    <t>Golden redhorse</t>
-  </si>
-  <si>
-    <t>Shorthead redhorse</t>
-  </si>
-  <si>
     <t xml:space="preserve">Goldfish </t>
   </si>
   <si>
-    <t xml:space="preserve">Golden shiner </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emerald shiner </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spottail shiner </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bluntnose minnow </t>
-  </si>
-  <si>
     <t>Rudd</t>
   </si>
   <si>
-    <t>Black bullhead</t>
-  </si>
-  <si>
-    <t>Brown bullhead</t>
-  </si>
-  <si>
-    <t>Channel catfish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">White perch </t>
-  </si>
-  <si>
-    <t>White bass</t>
-  </si>
-  <si>
-    <t>Rock bass</t>
-  </si>
-  <si>
     <t>Bluegill</t>
   </si>
   <si>
-    <t>Smallmouth bass</t>
-  </si>
-  <si>
-    <t>Largemouth bass</t>
-  </si>
-  <si>
-    <t>Black crappie</t>
-  </si>
-  <si>
     <t>Sunfish sp.</t>
   </si>
   <si>
-    <t>Yellow perch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Walleye (yellow pickerel) </t>
-  </si>
-  <si>
     <t>Logperch</t>
   </si>
   <si>
-    <t>Brook silverside</t>
-  </si>
-  <si>
-    <t>Freshwater drum</t>
-  </si>
-  <si>
     <t xml:space="preserve">Carp x Goldfish hybrid </t>
   </si>
   <si>
-    <t xml:space="preserve">Northern pike </t>
-  </si>
-  <si>
-    <t>Round goby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American eel </t>
-  </si>
-  <si>
     <t>F0076</t>
   </si>
   <si>
@@ -278,16 +197,142 @@
     <t>F0312</t>
   </si>
   <si>
-    <t>Rainbow trout</t>
-  </si>
-  <si>
-    <t>Atlantic salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Common shiner </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Green sunfish </t>
+    <t xml:space="preserve">Short Form </t>
+  </si>
+  <si>
+    <t>WE</t>
+  </si>
+  <si>
+    <t>YP</t>
+  </si>
+  <si>
+    <t>LMB</t>
+  </si>
+  <si>
+    <t>RB</t>
+  </si>
+  <si>
+    <t>WP</t>
+  </si>
+  <si>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>BB</t>
+  </si>
+  <si>
+    <t>GZ</t>
+  </si>
+  <si>
+    <t>BG</t>
+  </si>
+  <si>
+    <t>GF</t>
+  </si>
+  <si>
+    <t>PS</t>
+  </si>
+  <si>
+    <t>SMB</t>
+  </si>
+  <si>
+    <t>BSS</t>
+  </si>
+  <si>
+    <t>WS</t>
+  </si>
+  <si>
+    <t>Yellow Perch</t>
+  </si>
+  <si>
+    <t>Longnose Gar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gizzard Shad </t>
+  </si>
+  <si>
+    <t>Chinook Salmon</t>
+  </si>
+  <si>
+    <t>Rainbow Trout</t>
+  </si>
+  <si>
+    <t>Atlantic Salmon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Northern Pike </t>
+  </si>
+  <si>
+    <t xml:space="preserve">White Sucker </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bigmouth Buffalo </t>
+  </si>
+  <si>
+    <t>Golden Redhorse</t>
+  </si>
+  <si>
+    <t>Shorthead Redhorse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Golden Shiner </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emerald Shiner </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Common Shiner </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spottail Shiner </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bluntnose Minnow </t>
+  </si>
+  <si>
+    <t>Black Bullhead</t>
+  </si>
+  <si>
+    <t>Brown Bullhead</t>
+  </si>
+  <si>
+    <t>Channel Catfish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">American Eel </t>
+  </si>
+  <si>
+    <t xml:space="preserve">White Perch </t>
+  </si>
+  <si>
+    <t>White Bass</t>
+  </si>
+  <si>
+    <t>Rock Bass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Green Sunfish </t>
+  </si>
+  <si>
+    <t>Smallmouth Bass</t>
+  </si>
+  <si>
+    <t>Largemouth Bass</t>
+  </si>
+  <si>
+    <t>Black Crappie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walleye (Yellow Pickerel) </t>
+  </si>
+  <si>
+    <t>Brook Silverside</t>
+  </si>
+  <si>
+    <t>Round Goby</t>
+  </si>
+  <si>
+    <t>Freshwater Drum</t>
   </si>
 </sst>
 </file>
@@ -331,9 +376,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -668,346 +714,413 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1589E8ED-04D2-4E8E-811F-A5062083CB92}">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="21.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.453125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C1" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+        <v>74</v>
+      </c>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>3</v>
       </c>
       <c r="B15" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+        <v>79</v>
+      </c>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+        <v>81</v>
+      </c>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+        <v>84</v>
+      </c>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+        <v>87</v>
+      </c>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+        <v>91</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>26</v>
       </c>
       <c r="B30" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C30" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>27</v>
       </c>
       <c r="B31" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+      <c r="C34" s="2"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+      <c r="C35" s="2"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+        <v>96</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/01_data/01_raw_files/species_lookup.xlsx
+++ b/01_data/01_raw_files/species_lookup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RIZZUTOM\Desktop\GitHub Projects\2026_Reddick_fish_morphology\01_data\01_raw_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63CD4D69-65F9-4214-B365-C909A3FCCE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7025D36-80C1-4112-90CE-3D33F23018B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{E8ECBFDF-D715-470C-9FD4-9B764B132C4E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
   <si>
     <t xml:space="preserve">Common Name </t>
   </si>
@@ -155,9 +155,6 @@
     <t>F0601</t>
   </si>
   <si>
-    <t>Carp</t>
-  </si>
-  <si>
     <t>Pumpkinseed</t>
   </si>
   <si>
@@ -323,9 +320,6 @@
     <t>Black Crappie</t>
   </si>
   <si>
-    <t xml:space="preserve">Walleye (Yellow Pickerel) </t>
-  </si>
-  <si>
     <t>Brook Silverside</t>
   </si>
   <si>
@@ -333,6 +327,42 @@
   </si>
   <si>
     <t>Freshwater Drum</t>
+  </si>
+  <si>
+    <t>BW</t>
+  </si>
+  <si>
+    <t>RD</t>
+  </si>
+  <si>
+    <t>CC</t>
+  </si>
+  <si>
+    <t>Common Carp</t>
+  </si>
+  <si>
+    <t>NP</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>CHS</t>
+  </si>
+  <si>
+    <t>RG</t>
+  </si>
+  <si>
+    <t>LP</t>
+  </si>
+  <si>
+    <t>BF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walleye </t>
+  </si>
+  <si>
+    <t>FWD</t>
   </si>
 </sst>
 </file>
@@ -714,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1589E8ED-04D2-4E8E-811F-A5062083CB92}">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="21.26953125" bestFit="1" customWidth="1"/>
@@ -729,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -737,7 +767,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -745,7 +775,10 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>41</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -753,7 +786,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" s="2"/>
     </row>
@@ -762,10 +795,10 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -773,25 +806,29 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C8" s="2"/>
     </row>
@@ -800,19 +837,21 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="2"/>
+        <v>73</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -820,16 +859,18 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C12" s="2"/>
     </row>
@@ -838,7 +879,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C13" s="2"/>
     </row>
@@ -847,10 +888,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
@@ -858,16 +899,18 @@
         <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="2"/>
+        <v>100</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C16" s="2"/>
     </row>
@@ -876,16 +919,16 @@
         <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C17" s="2"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C18" s="2"/>
     </row>
@@ -894,7 +937,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C19" s="2"/>
     </row>
@@ -903,7 +946,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C20" s="2"/>
     </row>
@@ -912,16 +955,18 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C22" s="2"/>
     </row>
@@ -930,10 +975,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
@@ -941,7 +986,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C24" s="2"/>
     </row>
@@ -950,7 +995,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C25" s="2"/>
     </row>
@@ -959,10 +1004,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
@@ -970,7 +1015,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C27" s="2"/>
     </row>
@@ -979,21 +1024,21 @@
         <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
@@ -1001,10 +1046,10 @@
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
@@ -1012,10 +1057,10 @@
         <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
@@ -1023,10 +1068,10 @@
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
@@ -1034,10 +1079,10 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
@@ -1045,7 +1090,7 @@
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C34" s="2"/>
     </row>
@@ -1054,7 +1099,7 @@
         <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C35" s="2"/>
     </row>
@@ -1063,10 +1108,10 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
@@ -1074,10 +1119,10 @@
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
@@ -1085,7 +1130,10 @@
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>47</v>
+        <v>46</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
@@ -1093,10 +1141,10 @@
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
@@ -1104,7 +1152,10 @@
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>97</v>
+        <v>95</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
@@ -1112,7 +1163,10 @@
         <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>98</v>
+        <v>96</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
@@ -1120,8 +1174,11 @@
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>48</v>
-      </c>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C43" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
